--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_57_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_57_R6.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>2.0059</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3669</v>
+        <v>1.0483</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9869</v>
+        <v>0.9577</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1316</v>
+        <v>2.1158</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6589</v>
+        <v>-2.5953</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.7905</v>
+        <v>4.711</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8093</v>
+        <v>4.4966</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9107</v>
+        <v>-0.8501</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.1014</v>
+        <v>5.3466</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9409</v>
+        <v>-2.3808</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2518</v>
+        <v>-1.7452</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6891</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>3.9432</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4261</v>
+        <v>-1.7877</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.55</v>
+        <v>-1.183</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1239</v>
+        <v>-0.6047</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3943</v>
+        <v>1.214</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3943</v>
+        <v>1.214</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5124</v>
+        <v>1.5842</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2215</v>
+        <v>-0.3355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.291</v>
+        <v>1.9197</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3556</v>
+        <v>-1.1316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8872</v>
+        <v>1.6589</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4684</v>
+        <v>-2.7905</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2929</v>
+        <v>0.8093</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6133</v>
+        <v>2.9107</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6796</v>
+        <v>-2.1014</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9373</v>
+        <v>-1.9409</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7261</v>
+        <v>-1.2518</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2112</v>
+        <v>-0.6891</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.539</v>
+        <v>-0.4619</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8215</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2825</v>
+        <v>0.0567</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3929</v>
+        <v>1.4863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7377</v>
+        <v>1.2961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6552</v>
+        <v>0.1902</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1158</v>
+        <v>1.3556</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5953</v>
+        <v>0.8872</v>
       </c>
       <c r="I4" t="n">
-        <v>4.711</v>
+        <v>0.4684</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4966</v>
+        <v>3.2929</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8501</v>
+        <v>1.6133</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3466</v>
+        <v>1.6796</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3808</v>
+        <v>-1.9373</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7452</v>
+        <v>-0.7261</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.2112</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9432</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.4008</v>
+        <v>-0.5652</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4936</v>
+        <v>-0.7468</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9071</v>
+        <v>0.1817</v>
       </c>
       <c r="V4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.178</v>
+        <v>0.0108</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0747</v>
+        <v>-0.1568</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2527</v>
+        <v>0.1676</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6826</v>
+        <v>-0.0186</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3145</v>
+        <v>0.0349</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9971</v>
+        <v>-0.0535</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7863</v>
+        <v>0.0672</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0672</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1038</v>
+        <v>-0.0859</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3145</v>
+        <v>-0.0323</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2108</v>
+        <v>-0.0535</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8606</v>
+        <v>-0.2025</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7117</v>
+        <v>-0.224</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1489</v>
+        <v>0.0215</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.078</v>
+        <v>-0.3199</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1568</v>
+        <v>-0.4718</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2348</v>
+        <v>0.1519</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0186</v>
+        <v>-0.6826</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0349</v>
+        <v>0.3145</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0535</v>
+        <v>-0.9971</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0672</v>
+        <v>-0.7863</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0672</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.7863</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0859</v>
+        <v>0.1038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0323</v>
+        <v>0.3145</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1353</v>
+        <v>0.3626</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.3145</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0887</v>
+        <v>0.0481</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1648</v>
+        <v>-0.747</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2963</v>
+        <v>-1.8802</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8685</v>
+        <v>1.1332</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2779</v>
+        <v>2.2936</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6627</v>
+        <v>0.8415</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3848</v>
+        <v>1.4521</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5746</v>
+        <v>3.1839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.9361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>1.2479</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2966</v>
+        <v>-0.8903</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1249</v>
+        <v>-1.0945</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>0.2042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>4.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1876</v>
+        <v>-0.4865</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.4793</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0365</v>
+        <v>-0.0072</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.719</v>
+        <v>-0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6468</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2941</v>
+        <v>-1.1984</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6625</v>
+        <v>-0.2963</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3684</v>
+        <v>-0.9021</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2936</v>
+        <v>0.2779</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8415</v>
+        <v>0.6627</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4521</v>
+        <v>-0.3848</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1839</v>
+        <v>0.5746</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9361</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2479</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8903</v>
+        <v>-0.2966</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0945</v>
+        <v>0.1249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2042</v>
+        <v>-0.4216</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.1751</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0337</v>
+        <v>-0.2212</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2617</v>
+        <v>-0.224</v>
       </c>
       <c r="U8" t="n">
-        <v>0.228</v>
+        <v>0.0029</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9304</v>
+        <v>-1.719</v>
       </c>
       <c r="W8" t="n">
-        <v>1.214</v>
+        <v>-0.6468</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3159</v>
+        <v>-2.2692</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6311</v>
+        <v>-2.618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3152</v>
+        <v>0.3488</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7129</v>
@@ -1156,13 +1156,13 @@
         <v>3.0154</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9151</v>
+        <v>-0.0382</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0227</v>
+        <v>0.0358</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1076</v>
+        <v>-0.074</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.813</v>
+        <v>-2.4106</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2379</v>
+        <v>-1.3289</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4249</v>
+        <v>-1.0817</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1224</v>
+        <v>-1.7082</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.3601</v>
+        <v>0.3697</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2377</v>
+        <v>-2.0779</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.118</v>
+        <v>-0.2718</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.7805</v>
+        <v>-0.1947</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6625</v>
+        <v>-0.0771</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0044</v>
+        <v>-1.4364</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5796</v>
+        <v>0.5644</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4248</v>
+        <v>-2.0008</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.3917</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1598</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.5515</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.224</v>
+        <v>0.228</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1019</v>
+        <v>0.1928</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1221</v>
+        <v>0.0351</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1418</v>
+        <v>-0.9304</v>
       </c>
       <c r="W10" t="n">
         <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3274</v>
+        <v>-2.7383</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1113</v>
+        <v>-4.1632</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2162</v>
+        <v>1.4249</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7082</v>
+        <v>-4.1224</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3697</v>
+        <v>-4.3601</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0779</v>
+        <v>0.2377</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2718</v>
+        <v>-3.118</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1947</v>
+        <v>-3.7805</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0771</v>
+        <v>0.6625</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4364</v>
+        <v>-1.0044</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5644</v>
+        <v>-0.5796</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0008</v>
+        <v>-0.4248</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6888</v>
+        <v>-0.1494</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>-0.0272</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0993</v>
+        <v>-0.1221</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W11" t="n">
         <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6808</v>
+        <v>-3.4717</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4232</v>
+        <v>-2.3485</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2577</v>
+        <v>-1.1232</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3866</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3664</v>
+        <v>-0.1573</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2987</v>
+        <v>-0.224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.8147</v>
+        <v>-8.0679</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.0015</v>
+        <v>-11.2548</v>
       </c>
       <c r="F13" t="n">
-        <v>3.186700000000001</v>
+        <v>3.187</v>
       </c>
       <c r="G13" t="n">
         <v>-6.719999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.307100000000001</v>
+        <v>-3.3071</v>
       </c>
       <c r="I13" t="n">
         <v>-3.4129</v>
@@ -1456,10 +1456,10 @@
         <v>-4.902</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.3937</v>
+        <v>-7.393700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6391</v>
+        <v>4.639100000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.2367</v>
@@ -1468,13 +1468,13 @@
         <v>20.8758</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.226</v>
+        <v>-3.4793</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.830500000000001</v>
+        <v>-3.083800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3953</v>
+        <v>-0.3952</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5076</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1592</v>
+        <v>6.9506</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1155</v>
+        <v>4.7053</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0437</v>
+        <v>2.2454</v>
       </c>
       <c r="G14" t="n">
         <v>1.4836</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4867</v>
+        <v>0.3047</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9709</v>
+        <v>-0.3811</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4841</v>
+        <v>0.6858</v>
       </c>
       <c r="V14" t="n">
         <v>3.0748</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>S. WILBEKIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4967</v>
+        <v>4.9783</v>
       </c>
       <c r="E15" t="n">
-        <v>3.19</v>
+        <v>3.0796</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3067</v>
+        <v>1.8987</v>
       </c>
       <c r="G15" t="n">
-        <v>3.88</v>
+        <v>3.2306</v>
       </c>
       <c r="H15" t="n">
-        <v>0.611</v>
+        <v>-1.5641</v>
       </c>
       <c r="I15" t="n">
-        <v>3.269</v>
+        <v>4.7947</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5907</v>
+        <v>4.589</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8437</v>
+        <v>-0.3662</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7469</v>
+        <v>4.9552</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2893</v>
+        <v>-1.3584</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2327</v>
+        <v>-1.1979</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5221</v>
+        <v>-0.1605</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2946</v>
+        <v>0.405</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7591</v>
+        <v>-0.1177</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5355</v>
+        <v>0.5228</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>0.6468</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. WILBEKIN</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0804</v>
+        <v>4.5766</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6078</v>
+        <v>2.4823</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4726</v>
+        <v>2.0943</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2306</v>
+        <v>3.88</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5641</v>
+        <v>0.611</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7947</v>
+        <v>3.269</v>
       </c>
       <c r="J16" t="n">
-        <v>4.589</v>
+        <v>3.5907</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3662</v>
+        <v>0.8437</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9552</v>
+        <v>2.7469</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3584</v>
+        <v>0.2893</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1979</v>
+        <v>-0.2327</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1605</v>
+        <v>0.5221</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4929</v>
+        <v>0.3745</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>0.0514</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.3231</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6468</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6468</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6978</v>
+        <v>3.4505</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8955</v>
+        <v>1.4237</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8023</v>
+        <v>2.0268</v>
       </c>
       <c r="G17" t="n">
         <v>1.2432</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.666</v>
+        <v>0.4187</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9006</v>
+        <v>0.4288</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2346</v>
+        <v>-0.0101</v>
       </c>
       <c r="V17" t="n">
         <v>1.3247</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.43</v>
+        <v>2.1427</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3937</v>
+        <v>0.804</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0363</v>
+        <v>1.3387</v>
       </c>
       <c r="G18" t="n">
         <v>0.5577</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>1.393</v>
+        <v>1.1057</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9831</v>
+        <v>0.3934</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4099</v>
+        <v>0.7123</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7998</v>
+        <v>1.8905</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6142</v>
+        <v>1.8501</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1856</v>
+        <v>0.0404</v>
       </c>
       <c r="G19" t="n">
         <v>0.6234</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2306</v>
+        <v>0.3213</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2658</v>
+        <v>0.1206</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.071</v>
+        <v>0.5827</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0945</v>
+        <v>-0.4484</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1655</v>
+        <v>1.0311</v>
       </c>
       <c r="G20" t="n">
         <v>0.8772</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6008</v>
+        <v>1.1125</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5702</v>
+        <v>0.2164</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0306</v>
+        <v>0.8962</v>
       </c>
       <c r="V20" t="n">
         <v>1.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2671</v>
+        <v>0.1327</v>
       </c>
       <c r="E21" t="n">
         <v>-0.0379</v>
       </c>
       <c r="F21" t="n">
-        <v>0.305</v>
+        <v>0.1705</v>
       </c>
       <c r="G21" t="n">
         <v>0.1406</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1054</v>
+        <v>-0.2399</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0307</v>
+        <v>-0.1652</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1207</v>
+        <v>-3.8683</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9639</v>
+        <v>-2.846</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1567</v>
+        <v>-1.0223</v>
       </c>
       <c r="G22" t="n">
         <v>-2.842</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2091</v>
+        <v>0.0433</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7689</v>
+        <v>-4.8798</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8655</v>
+        <v>-7.6296</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0966</v>
+        <v>2.7498</v>
       </c>
       <c r="G23" t="n">
         <v>0.8103</v>
@@ -2248,13 +2248,13 @@
         <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7762</v>
+        <v>0.6653</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1766</v>
+        <v>0.0593</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9529</v>
+        <v>0.606</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7886</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2977</v>
+        <v>-6.3554</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.0418</v>
+        <v>-6.57</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.256</v>
+        <v>0.2145</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2846</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4411</v>
+        <v>0.5012</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2311</v>
+        <v>0.7016</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7886</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.814700000000002</v>
+        <v>9.601099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.186899999999999</v>
+        <v>-3.186900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0016</v>
+        <v>12.7879</v>
       </c>
       <c r="G25" t="n">
         <v>6.719999999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3071</v>
+        <v>3.307099999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>3.413</v>
+        <v>3.412999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>12.2955</v>
@@ -2395,7 +2395,7 @@
         <v>-3.9806</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.6388</v>
+        <v>-4.638799999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-20.8759</v>
@@ -2404,13 +2404,13 @@
         <v>16.2368</v>
       </c>
       <c r="S25" t="n">
-        <v>4.226</v>
+        <v>5.0123</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3953999999999999</v>
+        <v>0.3955000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.8308</v>
+        <v>4.617100000000001</v>
       </c>
       <c r="V25" t="n">
         <v>2.507600000000001</v>
